--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -97,45 +97,18 @@
     <t>GUERRA</t>
   </si>
   <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
     <t>PALMA</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
@@ -145,39 +118,15 @@
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>RANGEL</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>MONGE</t>
   </si>
   <si>
@@ -187,43 +136,16 @@
     <t>LUIS</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
+    <t>JOSE RAFAEL</t>
   </si>
   <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -691,7 +613,7 @@
         <v>91.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -786,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -812,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G9">
-        <v>78.38</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H9">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -874,16 +796,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>89.66</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -897,16 +822,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H3">
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -920,16 +848,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -943,16 +874,19 @@
         <v>45</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.56</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -966,16 +900,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.77</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -989,16 +926,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H7">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1012,16 +952,19 @@
         <v>37</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>37</v>
       </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>8.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1035,16 +978,19 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>91.89</v>
+      </c>
+      <c r="H9">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1100,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>86.20999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -1161,7 +1107,7 @@
         <v>91.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1178,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5">
-        <v>93.33</v>
+        <v>95.56</v>
       </c>
       <c r="H5">
         <v>8.300000000000001</v>
@@ -1204,16 +1150,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1239,7 +1185,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1256,16 +1202,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G8">
-        <v>86.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1282,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>78.38</v>
+        <v>91.89</v>
       </c>
       <c r="H9">
-        <v>6.9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1339,10 +1285,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1362,10 +1308,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1379,22 +1325,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920242</v>
+        <v>22330051920153</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1402,22 +1348,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920036</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1425,22 +1371,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920189</v>
+        <v>20330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1448,22 +1394,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920287</v>
+        <v>21330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1471,16 +1417,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920289</v>
+        <v>21330051920316</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1489,210 +1435,6 @@
         <v>17</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920337</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920323</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920267</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920268</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920276</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920279</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920292</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920306</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920316</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -91,64 +91,88 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SOTO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
   </si>
   <si>
     <t>LUIS</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -1046,16 +1070,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>89.66</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1072,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>97.62</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1098,16 +1122,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1124,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>95.56</v>
+        <v>82.22</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1150,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>96.77</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1185,7 +1209,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1228,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G9">
-        <v>91.89</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1247,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1279,16 +1303,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920010</v>
+        <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1302,16 +1326,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1325,22 +1349,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920153</v>
+        <v>22330051920017</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1348,16 +1372,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920242</v>
+        <v>22330051920333</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1371,22 +1395,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920235</v>
+        <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1394,22 +1418,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920323</v>
+        <v>22330051920317</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1417,24 +1441,93 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920316</v>
+        <v>22330051920084</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920116</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920036</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -103,27 +106,27 @@
     <t>AYOHUA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
@@ -148,6 +151,9 @@
     <t>DANIEL</t>
   </si>
   <si>
+    <t>EDER</t>
+  </si>
+  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
@@ -166,13 +172,13 @@
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1312,7 +1318,7 @@
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1326,7 +1332,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -1335,7 +1341,7 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1349,7 +1355,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1358,7 +1364,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1372,7 +1378,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920333</v>
+        <v>22330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
@@ -1381,13 +1387,13 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1395,7 +1401,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920054</v>
+        <v>22330051920333</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -1404,7 +1410,7 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1418,16 +1424,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920317</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1441,16 +1447,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920084</v>
+        <v>22330051920317</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1464,22 +1470,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920189</v>
+        <v>22330051920084</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1490,13 +1496,13 @@
         <v>22330051920116</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1513,13 +1519,13 @@
         <v>22330051920036</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1528,6 +1534,29 @@
         <v>14</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920189</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>
